--- a/phases/0-setup/대한민국 구석구석 추천 경로.xlsx
+++ b/phases/0-setup/대한민국 구석구석 추천 경로.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlaeh\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlaeh\OneDrive\바탕 화면\Projects\travel\phases\0-setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E88E317-2360-42E0-8E4C-4F9967691DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96487BE5-6638-4FDC-B7C6-2EA5C4A07490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12108" yWindow="456" windowWidth="10512" windowHeight="11508" xr2:uid="{40A227AC-43D2-40F5-B4D3-45C1167407AE}"/>
+    <workbookView xWindow="11280" yWindow="780" windowWidth="10512" windowHeight="11508" xr2:uid="{40A227AC-43D2-40F5-B4D3-45C1167407AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
